--- a/outputs/41589.xlsx
+++ b/outputs/41589.xlsx
@@ -154,28 +154,32 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -432,441 +436,441 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="66.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="66.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="2" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5" t="n">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="n">
         <v>44466</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>44466</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="str">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="str">
         <f aca="true">IF(AND(H4&gt;=TODAY()-30,I4="YES"),"HOLD",IF(AND(H4&lt;TODAY()-30,I4="YES"),"TOUCH BASE","NO ACTION"))</f>
         <v>NO ACTION</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -887,29 +891,29 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/outputs/41589.xlsx
+++ b/outputs/41589.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="str">
-        <f aca="true">IF(AND(H4&gt;=TODAY()-30,I4="YES"),"HOLD",IF(AND(H4&lt;TODAY()-30,I4="YES"),"TOUCH BASE","NO ACTION"))</f>
+        <f aca="false">IF(AND(I4="YES",H4&gt;=K1-30),"HOLD",IF(AND(I4="YES",H4&lt;K1-30),"TOUCH BASE","NO ACTION"))</f>
         <v>NO ACTION</v>
       </c>
     </row>
